--- a/backend/chunking/Retrieval_Benchmark.xlsx
+++ b/backend/chunking/Retrieval_Benchmark.xlsx
@@ -488,31 +488,31 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.2</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.1</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.13333</v>
+        <v>0.26666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>29.258</v>
+        <v>26.472</v>
       </c>
       <c r="J2" t="n">
-        <v>29.855</v>
+        <v>28.392</v>
       </c>
     </row>
     <row r="3">
@@ -522,31 +522,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.475</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.15</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.35</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="I3" t="n">
-        <v>30.173</v>
+        <v>24.61555555555556</v>
       </c>
       <c r="J3" t="n">
-        <v>30.901</v>
+        <v>27.50777777777778</v>
       </c>
     </row>
     <row r="4">
@@ -556,31 +556,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7</v>
+        <v>0.875</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.65</v>
+        <v>0.8125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.30833</v>
+        <v>0.3854125</v>
       </c>
       <c r="H4" t="n">
-        <v>2.54</v>
+        <v>2.505</v>
       </c>
       <c r="I4" t="n">
-        <v>33.47</v>
+        <v>25.92875</v>
       </c>
       <c r="J4" t="n">
-        <v>31.012</v>
+        <v>30.6625</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>30.36</v>
       </c>
       <c r="L2" t="n">
-        <v>31</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="3">
@@ -752,13 +752,13 @@
         <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>36.52</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="4">
@@ -799,10 +799,10 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L4" t="n">
-        <v>31.51</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="5">
@@ -813,12 +813,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trường Đại học Công nghiệp Thành phố Hồ Chí Minh có truyền thống đào tạo bao nhiêu năm?</t>
+          <t>Nếu cần hỗ trợ kỹ thuật, sinh viên có thể gọi số điện thoại nào?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>b78da5dc-57ea-453a-8501-195d9d5c2533</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -843,10 +843,10 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>32.01</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="6">
@@ -857,51 +857,51 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nhà trường nhận Huân chương Độc lập Hạng 3 vào năm nào?</t>
+          <t>Phòng Công tác Chính trị và Hỗ trợ Sinh viên có thể được liên hệ qua số máy nhánh nào?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>2f60b360-629f-4c6c-9b49-90758f90fcfe</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>23.51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nhà trường nhận Huân chương Lao động Hạng 1 vào năm nào?</t>
+          <t>Trường có chấp nhận bằng TOEFL iBT phiên bản làm tại nhà không?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,30 +931,30 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>23.51</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lịch khám sức khỏe cho sinh viên K19 và K20 được thông báo vào ngày nào?</t>
+          <t>Sinh viên muốn nộp chứng chỉ tiếng Anh thi bên ngoài thì nên thi ở những chỗ nào để được công nhận?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>d20bdaf1-ee0e-4c92-9989-410e7fdc8186</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -975,30 +975,30 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>26.55</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nếu cần hỗ trợ kỹ thuật, sinh viên có thể gọi số điện thoại nào?</t>
+          <t>Chỗ nào cung cấp thông tin về các hoạt động giao lưu quốc tế của trường?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>b78da5dc-57ea-453a-8501-195d9d5c2533</t>
+          <t>33e3e9b8-dc92-4941-9c25-efb77d2c9629</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1019,26 +1019,26 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>26.52</v>
       </c>
       <c r="L9" t="n">
-        <v>27.01</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phòng Công tác Chính trị và Hỗ trợ Sinh viên có thể được liên hệ qua số máy nhánh nào?</t>
+          <t>Thông báo về việc đóng bảo hiểm y tế cuối năm 2025 cho sinh viên khóa mới nhất được đăng khi nào?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2f60b360-629f-4c6c-9b49-90758f90fcfe</t>
+          <t>fbae1105-243e-4c6a-8a7a-d0630a4d7e62</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1051,38 +1051,38 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>34.51</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Website Cẩm nang người học do đơn vị nào phát triển?</t>
+          <t>Trang web nào để sinh viên xem thông tin về Ký túc xá?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>4b3c6c71-de93-4935-9aca-e2936c59323b</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1107,10 +1107,10 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>26.51</v>
       </c>
       <c r="L11" t="n">
-        <v>26.51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -1121,40 +1121,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trường có chấp nhận bằng TOEFL iBT phiên bản làm tại nhà không?</t>
+          <t>Sự kiện chào đón tân sinh viên năm 2025 được nhà trường ra thông báo vào thời gian nào?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>f60c4002-17b0-4182-8ae1-0dfb35381b3b</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="13">
@@ -1165,40 +1165,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sinh viên muốn nộp chứng chỉ tiếng Anh thi bên ngoài thì nên thi ở những chỗ nào để được công nhận?</t>
+          <t>Thư chúc mừng tân sinh viên đầu năm học là do ai viết?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>d20bdaf1-ee0e-4c92-9989-410e7fdc8186</t>
+          <t>d5ddf6a3-ac7f-4b05-abc9-2144ee1fd93b</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>28.51</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
-        <v>32.39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chuyên trang Cẩm nang người học có bao nhiêu nhóm thông tin chính để sinh viên tra cứu?</t>
+          <t>Sinh viên có thể tìm mã khoa của mình ở đâu?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>a00cfd41-5a06-41d6-b42f-7a9f447e4d4c</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1236,13 +1236,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>45.69</v>
+        <v>26</v>
       </c>
       <c r="L14" t="n">
-        <v>32.09</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="15">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chỗ nào cung cấp thông tin về các hoạt động giao lưu quốc tế của trường?</t>
+          <t>Sinh viên ngành Kế toán, Kiểm toán thuộc viện nào quản lý?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>33e3e9b8-dc92-4941-9c25-efb77d2c9629</t>
+          <t>3f76f009-4910-4411-a9f8-8b4980b9b97d</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1268,41 +1268,41 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L15" t="n">
-        <v>33.01</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thông báo về việc đóng bảo hiểm y tế cuối năm 2025 cho sinh viên khóa mới nhất được đăng khi nào?</t>
+          <t>Điểm TOEFL iBT 94 tương đương với khung CEFR nào và mức VSTEP tương ứng là bao nhiêu?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fbae1105-243e-4c6a-8a7a-d0630a4d7e62</t>
+          <t>6754b800-d1ae-49cc-8387-d88c880a890c</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1324,205 +1324,205 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>32.51</v>
+        <v>27.01</v>
       </c>
       <c r="L16" t="n">
-        <v>31</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trang web nào để sinh viên xem thông tin về Ký túc xá?</t>
+          <t>Ngành Quản trị kinh doanh và ngành Marketing của Khoa Quản trị kinh doanh có sinh hoạt đầu khóa cùng một ngày không?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4b3c6c71-de93-4935-9aca-e2936c59323b</t>
+          <t>3f76f009-4910-4411-a9f8-8b4980b9b97d</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>29.51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sự kiện chào đón tân sinh viên năm 2025 được nhà trường ra thông báo vào thời gian nào?</t>
+          <t>Khoa Công nghệ Điện tử và Khoa Công nghệ Hóa học có tổ chức sinh hoạt đầu khóa vào cùng một ngày không?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>f60c4002-17b0-4182-8ae1-0dfb35381b3b</t>
+          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>27</v>
+        <v>27.52</v>
       </c>
       <c r="L18" t="n">
-        <v>27</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thư chúc mừng tân sinh viên đầu năm học là do ai viết?</t>
+          <t>Khoa Ngoại ngữ và Khoa Công nghệ May - Thời trang, khoa nào tổ chức sinh hoạt đầu khóa sớm hơn?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>d5ddf6a3-ac7f-4b05-abc9-2144ee1fd93b</t>
+          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="K19" t="n">
-        <v>28.51</v>
+        <v>30.37</v>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sinh viên có thể tìm mã khoa của mình ở đâu?</t>
+          <t>Sinh hoạt đầu khoá của Khoa Công nghệ Cơ khí và Khoa Công nghệ Động lực diễn ra vào ngày nào?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>a00cfd41-5a06-41d6-b42f-7a9f447e4d4c</t>
+          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>31.01</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sinh viên ngành Kế toán, Kiểm toán thuộc viện nào quản lý?</t>
+          <t>Khoa Công nghệ Điện và Khoa Công nghệ Thông tin tổ chức sinh hoạt vào ngày nào?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3f76f009-4910-4411-a9f8-8b4980b9b97d</t>
+          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1535,22 +1535,22 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="K21" t="n">
-        <v>29.51</v>
+        <v>25.01</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="22">
@@ -1561,40 +1561,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Điểm TOEFL iBT 94 tương đương với khung CEFR nào và mức VSTEP tương ứng là bao nhiêu?</t>
+          <t>Viện Tài chính - Kế toán tổ chức sinh hoạt cho ngành Kế toán, Kiểm toán và ngành Tài chính - Ngân hàng có cùng thời gian không?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6754b800-d1ae-49cc-8387-d88c880a890c</t>
+          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L22" t="n">
-        <v>25.51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1605,392 +1605,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hình ảnh nhập học của Tân sinh viên K21 được chụp liên tục trong bao nhiêu ngày kể từ 23/08/2025?</t>
+          <t>Khoa Luật và Khoa học chính trị sinh hoạt đầu khóa trước hay sau ngày ra thông báo Ngày hội Chào Tân sinh viên 2025?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
+          <t>f60c4002-17b0-4182-8ae1-0dfb35381b3b</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>39.71</v>
+        <v>28.52</v>
       </c>
       <c r="L23" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ngành Quản trị kinh doanh và ngành Marketing của Khoa Quản trị kinh doanh có sinh hoạt đầu khóa cùng một ngày không?</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3f76f009-4910-4411-a9f8-8b4980b9b97d</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="L24" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Khoa Công nghệ Điện tử và Khoa Công nghệ Hóa học có tổ chức sinh hoạt đầu khóa vào cùng một ngày không?</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>27</v>
-      </c>
-      <c r="L25" t="n">
-        <v>32.51</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Khoa Ngoại ngữ và Khoa Công nghệ May - Thời trang, khoa nào tổ chức sinh hoạt đầu khóa sớm hơn?</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>29</v>
-      </c>
-      <c r="L26" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Sinh hoạt đầu khoá của Khoa Công nghệ Cơ khí và Khoa Công nghệ Động lực diễn ra vào ngày nào?</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>30.51</v>
-      </c>
-      <c r="L27" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Khoa Công nghệ Điện và Khoa Công nghệ Thông tin tổ chức sinh hoạt vào ngày nào?</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>28</v>
-      </c>
-      <c r="L28" t="n">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Viện Tài chính - Kế toán tổ chức sinh hoạt cho ngành Kế toán, Kiểm toán và ngành Tài chính - Ngân hàng có cùng thời gian không?</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>299155ce-7c1e-4da0-9e2b-596308c37ac0</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="L29" t="n">
-        <v>35.01</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Khoa Luật và Khoa học chính trị sinh hoạt đầu khóa trước hay sau ngày ra thông báo Ngày hội Chào Tân sinh viên 2025?</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>f60c4002-17b0-4182-8ae1-0dfb35381b3b</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="L30" t="n">
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Khoa Thương mại và Du lịch sinh hoạt đầu khóa vào ngày nào và thông báo khám sức khỏe K19, K20 có trước đó mấy ngày?</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>NOT_FOUND_THIEU_DATA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>39</v>
-      </c>
-      <c r="L31" t="n">
-        <v>32.19</v>
+        <v>26.01</v>
       </c>
     </row>
   </sheetData>
